--- a/artfynd/A 24701-2023 artfynd.xlsx
+++ b/artfynd/A 24701-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24701-2023 artfynd.xlsx
+++ b/artfynd/A 24701-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106123507</v>
+        <v>106118322</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620378.252465531</v>
+        <v>620378</v>
       </c>
       <c r="R2" t="n">
-        <v>6351923.939266603</v>
+        <v>6351924</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106123508</v>
+        <v>106118323</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620494.2020822495</v>
+        <v>620494</v>
       </c>
       <c r="R3" t="n">
-        <v>6352033.851985551</v>
+        <v>6352034</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,19 +862,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,12 +898,7 @@
         <v>106119958</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620483.9802656148</v>
+        <v>620484</v>
       </c>
       <c r="R4" t="n">
-        <v>6352013.007205558</v>
+        <v>6352013</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,19 +972,9 @@
           <t>2022-03-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 24701-2023 artfynd.xlsx
+++ b/artfynd/A 24701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118322</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118323</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>